--- a/july 2026/GT_JULY_26/24-07-26/Zeshan.xlsx
+++ b/july 2026/GT_JULY_26/24-07-26/Zeshan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761E75F7-7FE5-4EEB-9475-109CC5873D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B57742-E137-4026-81BE-ED3B6908C069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53672,7 +53672,7 @@
       </c>
       <c r="T5" s="301">
         <f>+'3'!P35</f>
-        <v>10015.067480949152</v>
+        <v>0</v>
       </c>
       <c r="XEX5" t="s">
         <v>106</v>
@@ -54224,39 +54224,39 @@
       </c>
       <c r="H13" s="286">
         <f>+'1'!H22+'2'!H22+'3'!H22+'4'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22+'17'!H22+'18'!H22+'19'!H22+'20'!H22+'21'!H22+'22'!H22+'23'!H22+'24'!H22+'25'!H22+'26'!H22+'27'!H22+'28'!H22+'29'!H22+'30'!H22</f>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I13" s="236">
         <f t="shared" si="0"/>
-        <v>9415.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="J13" s="286">
         <f>+'1'!J22+'2'!J22+'3'!J22+'4'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22+'19'!J22+'20'!J22+'21'!J22+'22'!J22+'23'!J22+'24'!J22+'25'!J22+'26'!J22+'27'!J22+'28'!J22+'29'!J22+'30'!J22</f>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="K13" s="286">
         <f>+'1'!K22+'2'!K22+'3'!K22+'4'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22+'11'!K22+'12'!K22+'13'!K22+'14'!K22+'15'!K22+'16'!K22+'17'!K22+'18'!K22+'19'!K22+'20'!K22+'21'!K22+'22'!K22+'23'!K22+'24'!K22+'25'!K22+'26'!K22+'27'!K22+'28'!K22+'29'!K22+'30'!K22</f>
-        <v>329.53200000000004</v>
+        <v>0</v>
       </c>
       <c r="L13" s="286">
         <f>+'1'!L22+'2'!L22+'3'!L22+'4'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22+'11'!L22+'12'!L22+'13'!L22+'14'!L22+'15'!L22+'16'!L22+'17'!L22+'18'!L22+'19'!L22+'20'!L22+'21'!L22+'22'!L22+'23'!L22+'24'!L22+'25'!L22+'26'!L22+'27'!L22+'28'!L22+'29'!L22+'30'!L22</f>
-        <v>480.17520000000002</v>
+        <v>0</v>
       </c>
       <c r="M13" s="230">
         <f t="shared" si="1"/>
-        <v>8134.7328000000007</v>
+        <v>0</v>
       </c>
       <c r="N13" s="286">
         <f>+'1'!N22+'2'!N22+'3'!N22+'4'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22+'11'!N22+'12'!N22+'13'!N22+'14'!N22+'15'!N22+'16'!N22+'17'!N22+'18'!N22+'19'!N22+'20'!N22+'21'!N22+'22'!N22+'23'!N22+'24'!N22+'25'!N22+'26'!N22+'27'!N22+'28'!N22+'29'!N22+'30'!N22</f>
-        <v>1830.5084745762701</v>
+        <v>0</v>
       </c>
       <c r="O13" s="286">
         <f>+'1'!O22+'2'!O22+'3'!O22+'4'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22+'11'!O22+'12'!O22+'13'!O22+'14'!O22+'15'!O22+'16'!O22+'17'!O22+'18'!O22+'19'!O22+'20'!O22+'21'!O22+'22'!O22+'23'!O22+'24'!O22+'25'!O22+'26'!O22+'27'!O22+'28'!O22+'29'!O22+'30'!O22</f>
-        <v>49.826206372881352</v>
+        <v>0</v>
       </c>
       <c r="P13" s="119">
         <f t="shared" si="2"/>
-        <v>10015.067480949152</v>
+        <v>0</v>
       </c>
       <c r="R13" s="299">
         <v>11</v>
@@ -54440,39 +54440,39 @@
       </c>
       <c r="H16" s="113">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>21037.599999999999</v>
+        <v>11622.4</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>1400.5519999999999</v>
+        <v>929.79199999999992</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>736.31600000000003</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
-        <v>480.17520000000002</v>
+        <v>0</v>
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>18420.556800000002</v>
+        <v>10285.824000000001</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>4027.1186440677957</v>
+        <v>2196.6101694915255</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>112.23837722033898</v>
+        <v>62.412170847457631</v>
       </c>
       <c r="P16" s="234">
         <f>SUM(P7:P15)</f>
-        <v>22559.913821288137</v>
+        <v>12544.846340338983</v>
       </c>
       <c r="R16" s="299">
         <v>14</v>
@@ -54555,7 +54555,7 @@
       <c r="O19" s="369"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>21037.599999999999</v>
+        <v>11622.4</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -54587,7 +54587,7 @@
       <c r="O20" s="371"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>1400.5519999999999</v>
+        <v>929.79199999999992</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -54619,7 +54619,7 @@
       <c r="O21" s="371"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>1216.4911999999999</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -54652,7 +54652,7 @@
       <c r="O22" s="371"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>18420.556799999998</v>
+        <v>10285.824000000001</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -54687,7 +54687,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>4027.1186440677957</v>
+        <v>2196.6101694915255</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -54720,7 +54720,7 @@
       <c r="O24" s="373"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>22447.675444067794</v>
+        <v>12482.434169491526</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -54756,7 +54756,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>112.23837722033898</v>
+        <v>62.412170847457631</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -54777,7 +54777,7 @@
       <c r="O26" s="331"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>22559.913821288133</v>
+        <v>12544.846340338983</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -54891,7 +54891,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>22559.913821288137</v>
+        <v>12544.846340338983</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -58633,40 +58633,41 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="287"/>
-      <c r="H22" s="96">
-        <v>240</v>
-      </c>
+      <c r="H22" s="96"/>
       <c r="I22" s="236">
         <f t="shared" si="0"/>
-        <v>9415.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="J22" s="272">
         <f t="shared" si="1"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="K22" s="128">
         <f t="shared" si="1"/>
-        <v>329.53200000000004</v>
+        <v>0</v>
       </c>
       <c r="L22" s="119">
         <f t="shared" si="1"/>
-        <v>480.17520000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="230">
         <f t="shared" si="2"/>
-        <v>8134.7328000000007</v>
+        <v>0</v>
       </c>
       <c r="N22" s="277">
         <f t="shared" si="3"/>
-        <v>1830.5084745762701</v>
+        <v>0</v>
       </c>
       <c r="O22" s="239">
         <f t="shared" si="4"/>
-        <v>49.826206372881352</v>
+        <v>0</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="5"/>
-        <v>10015.067480949152</v>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>240</v>
       </c>
       <c r="S22" s="269">
         <v>0.05</v>
@@ -58848,39 +58849,39 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>9415.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>329.53200000000004</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
-        <v>480.17520000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>8134.7328000000007</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1830.5084745762701</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>49.826206372881352</v>
+        <v>0</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>10015.067480949152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -58930,7 +58931,7 @@
       <c r="O28" s="369"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>9415.2000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58951,7 +58952,7 @@
       <c r="O29" s="371"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58972,7 +58973,7 @@
       <c r="O30" s="371"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>809.70720000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58994,7 +58995,7 @@
       <c r="O31" s="371"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>8134.7328000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59018,7 +59019,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1830.5084745762701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59040,7 +59041,7 @@
       <c r="O33" s="373"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>9965.2412745762704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59065,7 +59066,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>49.826206372881352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59075,7 +59076,7 @@
       <c r="O35" s="331"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>10015.067480949152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
